--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273840</v>
+        <v>113273841</v>
       </c>
       <c r="B2" t="n">
-        <v>78131</v>
+        <v>78147</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535456</v>
+        <v>535444</v>
       </c>
       <c r="R2" t="n">
-        <v>6624534</v>
+        <v>6624456</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113273781</v>
+        <v>113273882</v>
       </c>
       <c r="B3" t="n">
-        <v>78697</v>
+        <v>77792</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273882</v>
+        <v>113273781</v>
       </c>
       <c r="B4" t="n">
-        <v>77776</v>
+        <v>78713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -986,7 +986,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273841</v>
+        <v>113273840</v>
       </c>
       <c r="B5" t="n">
-        <v>78131</v>
+        <v>78147</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535444</v>
+        <v>535456</v>
       </c>
       <c r="R5" t="n">
-        <v>6624456</v>
+        <v>6624534</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273841</v>
+        <v>113273840</v>
       </c>
       <c r="B2" t="n">
         <v>78147</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535444</v>
+        <v>535456</v>
       </c>
       <c r="R2" t="n">
-        <v>6624456</v>
+        <v>6624534</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113273882</v>
+        <v>113273841</v>
       </c>
       <c r="B3" t="n">
-        <v>77792</v>
+        <v>78147</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535449</v>
+        <v>535444</v>
       </c>
       <c r="R3" t="n">
-        <v>6624543</v>
+        <v>6624456</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273840</v>
+        <v>113273882</v>
       </c>
       <c r="B5" t="n">
-        <v>78147</v>
+        <v>77792</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535456</v>
+        <v>535449</v>
       </c>
       <c r="R5" t="n">
-        <v>6624534</v>
+        <v>6624543</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273840</v>
+        <v>113273882</v>
       </c>
       <c r="B2" t="n">
-        <v>78147</v>
+        <v>77804</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535456</v>
+        <v>535449</v>
       </c>
       <c r="R2" t="n">
-        <v>6624534</v>
+        <v>6624543</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113273841</v>
+        <v>113273781</v>
       </c>
       <c r="B3" t="n">
-        <v>78147</v>
+        <v>78725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535444</v>
+        <v>535449</v>
       </c>
       <c r="R3" t="n">
-        <v>6624456</v>
+        <v>6624543</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273781</v>
+        <v>113273840</v>
       </c>
       <c r="B4" t="n">
-        <v>78713</v>
+        <v>78159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535449</v>
+        <v>535456</v>
       </c>
       <c r="R4" t="n">
-        <v>6624543</v>
+        <v>6624534</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273882</v>
+        <v>113273841</v>
       </c>
       <c r="B5" t="n">
-        <v>77792</v>
+        <v>78159</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535449</v>
+        <v>535444</v>
       </c>
       <c r="R5" t="n">
-        <v>6624543</v>
+        <v>6624456</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273882</v>
+        <v>113273841</v>
       </c>
       <c r="B2" t="n">
-        <v>77804</v>
+        <v>78159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535449</v>
+        <v>535444</v>
       </c>
       <c r="R2" t="n">
-        <v>6624543</v>
+        <v>6624456</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113273781</v>
+        <v>113273840</v>
       </c>
       <c r="B3" t="n">
-        <v>78725</v>
+        <v>78159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535449</v>
+        <v>535456</v>
       </c>
       <c r="R3" t="n">
-        <v>6624543</v>
+        <v>6624534</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273840</v>
+        <v>113273781</v>
       </c>
       <c r="B4" t="n">
-        <v>78159</v>
+        <v>78725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535456</v>
+        <v>535449</v>
       </c>
       <c r="R4" t="n">
-        <v>6624534</v>
+        <v>6624543</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273841</v>
+        <v>113273882</v>
       </c>
       <c r="B5" t="n">
-        <v>78159</v>
+        <v>77804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535444</v>
+        <v>535449</v>
       </c>
       <c r="R5" t="n">
-        <v>6624456</v>
+        <v>6624543</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273841</v>
+        <v>113273781</v>
       </c>
       <c r="B2" t="n">
-        <v>78159</v>
+        <v>78747</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535444</v>
+        <v>535449</v>
       </c>
       <c r="R2" t="n">
-        <v>6624456</v>
+        <v>6624543</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,7 +789,7 @@
         <v>113273840</v>
       </c>
       <c r="B3" t="n">
-        <v>78159</v>
+        <v>78181</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273781</v>
+        <v>113273882</v>
       </c>
       <c r="B4" t="n">
-        <v>78725</v>
+        <v>77826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -986,7 +986,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273882</v>
+        <v>113273841</v>
       </c>
       <c r="B5" t="n">
-        <v>77804</v>
+        <v>78181</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535449</v>
+        <v>535444</v>
       </c>
       <c r="R5" t="n">
-        <v>6624543</v>
+        <v>6624456</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273781</v>
+        <v>113273882</v>
       </c>
       <c r="B2" t="n">
-        <v>78747</v>
+        <v>77829</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -764,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113273840</v>
+        <v>113273781</v>
       </c>
       <c r="B3" t="n">
-        <v>78181</v>
+        <v>78751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535456</v>
+        <v>535449</v>
       </c>
       <c r="R3" t="n">
-        <v>6624534</v>
+        <v>6624543</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273882</v>
+        <v>113273841</v>
       </c>
       <c r="B4" t="n">
-        <v>77826</v>
+        <v>78184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535449</v>
+        <v>535444</v>
       </c>
       <c r="R4" t="n">
-        <v>6624543</v>
+        <v>6624456</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273841</v>
+        <v>113273840</v>
       </c>
       <c r="B5" t="n">
-        <v>78181</v>
+        <v>78184</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535444</v>
+        <v>535456</v>
       </c>
       <c r="R5" t="n">
-        <v>6624456</v>
+        <v>6624534</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273882</v>
+        <v>113273841</v>
       </c>
       <c r="B2" t="n">
-        <v>77829</v>
+        <v>78184</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535449</v>
+        <v>535444</v>
       </c>
       <c r="R2" t="n">
-        <v>6624543</v>
+        <v>6624456</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113273781</v>
+        <v>113273840</v>
       </c>
       <c r="B3" t="n">
-        <v>78751</v>
+        <v>78184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535449</v>
+        <v>535456</v>
       </c>
       <c r="R3" t="n">
-        <v>6624543</v>
+        <v>6624534</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273841</v>
+        <v>113273882</v>
       </c>
       <c r="B4" t="n">
-        <v>78184</v>
+        <v>77829</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535444</v>
+        <v>535449</v>
       </c>
       <c r="R4" t="n">
-        <v>6624456</v>
+        <v>6624543</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273840</v>
+        <v>113273781</v>
       </c>
       <c r="B5" t="n">
-        <v>78184</v>
+        <v>78751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535456</v>
+        <v>535449</v>
       </c>
       <c r="R5" t="n">
-        <v>6624534</v>
+        <v>6624543</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113273841</v>
       </c>
       <c r="B2" t="n">
-        <v>78184</v>
+        <v>78190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113273840</v>
+        <v>113273781</v>
       </c>
       <c r="B3" t="n">
-        <v>78184</v>
+        <v>78757</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535456</v>
+        <v>535449</v>
       </c>
       <c r="R3" t="n">
-        <v>6624534</v>
+        <v>6624543</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -900,7 +900,7 @@
         <v>113273882</v>
       </c>
       <c r="B4" t="n">
-        <v>77829</v>
+        <v>77835</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273781</v>
+        <v>113273840</v>
       </c>
       <c r="B5" t="n">
-        <v>78751</v>
+        <v>78190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535449</v>
+        <v>535456</v>
       </c>
       <c r="R5" t="n">
-        <v>6624543</v>
+        <v>6624534</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273841</v>
+        <v>113273882</v>
       </c>
       <c r="B2" t="n">
-        <v>78190</v>
+        <v>77835</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535444</v>
+        <v>535449</v>
       </c>
       <c r="R2" t="n">
-        <v>6624456</v>
+        <v>6624543</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273882</v>
+        <v>113273840</v>
       </c>
       <c r="B4" t="n">
-        <v>77835</v>
+        <v>78190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535449</v>
+        <v>535456</v>
       </c>
       <c r="R4" t="n">
-        <v>6624543</v>
+        <v>6624534</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273840</v>
+        <v>113273841</v>
       </c>
       <c r="B5" t="n">
         <v>78190</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535456</v>
+        <v>535444</v>
       </c>
       <c r="R5" t="n">
-        <v>6624534</v>
+        <v>6624456</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273882</v>
+        <v>113273841</v>
       </c>
       <c r="B2" t="n">
-        <v>77835</v>
+        <v>78197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535449</v>
+        <v>535444</v>
       </c>
       <c r="R2" t="n">
-        <v>6624543</v>
+        <v>6624456</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,7 +789,7 @@
         <v>113273781</v>
       </c>
       <c r="B3" t="n">
-        <v>78757</v>
+        <v>78764</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113273840</v>
+        <v>113273882</v>
       </c>
       <c r="B4" t="n">
-        <v>78190</v>
+        <v>77842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535456</v>
+        <v>535449</v>
       </c>
       <c r="R4" t="n">
-        <v>6624534</v>
+        <v>6624543</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113273841</v>
+        <v>113273840</v>
       </c>
       <c r="B5" t="n">
-        <v>78190</v>
+        <v>78197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535444</v>
+        <v>535456</v>
       </c>
       <c r="R5" t="n">
-        <v>6624456</v>
+        <v>6624534</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 29457-2020 artfynd.xlsx
+++ b/artfynd/A 29457-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
